--- a/output/pdf_financials_xlsx/MSV.xlsx
+++ b/output/pdf_financials_xlsx/MSV.xlsx
@@ -1068,34 +1068,34 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.125569</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.703224</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.865478</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.806038</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.980945</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.9112130000000001</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.521021</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.637478</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>1.356351</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>2.216988</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>3.189903</v>
@@ -2063,34 +2063,34 @@
         <v>-4.601133</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.465415</v>
+        <v>-4.590984</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.970842</v>
+        <v>-6.674066</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-4.67655</v>
+        <v>-5.542028</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.987033</v>
+        <v>-3.793071</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.665516</v>
+        <v>-2.646461</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>6.680947</v>
+        <v>5.769734</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.407668</v>
+        <v>-2.928689</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-5.205216</v>
+        <v>-5.842694</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.170695</v>
+        <v>-1.527046</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-60.293846</v>
+        <v>-62.510834</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-4.159345</v>
@@ -2185,34 +2185,34 @@
         <v>-4.601133</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.465415</v>
+        <v>-4.590984</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.970842</v>
+        <v>-6.674066</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.67655</v>
+        <v>-5.542028</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.987033</v>
+        <v>-3.793071</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.665516</v>
+        <v>-2.646461</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>6.680947</v>
+        <v>5.769734</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.407668</v>
+        <v>-2.928689</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-5.205216</v>
+        <v>-5.842694</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.170695</v>
+        <v>-1.527046</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-60.293846</v>
+        <v>-62.510834</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-4.159345</v>
@@ -46944,7 +46944,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -54288,7 +54288,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -55194,7 +55194,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">

--- a/output/pdf_financials_xlsx/MSV.xlsx
+++ b/output/pdf_financials_xlsx/MSV.xlsx
@@ -7549,13 +7549,13 @@
         <v>0</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.014827</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.016359</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.001113</v>
       </c>
       <c r="O112" s="3" t="n">
         <v>0</v>
@@ -32264,7 +32264,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -34464,7 +34468,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MSV.xlsx
+++ b/output/pdf_financials_xlsx/MSV.xlsx
@@ -754,58 +754,58 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.755584</v>
+        <v>0.8124169999999999</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.779881</v>
+        <v>0.835131</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.561191</v>
+        <v>0.621691</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.83549</v>
+        <v>1.266316</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.810156</v>
+        <v>1.265363</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.603082</v>
+        <v>1.144698</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.466155</v>
+        <v>1.129231</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.372086</v>
+        <v>1.185754</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.392841</v>
+        <v>1.369821</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.483509</v>
+        <v>1.025031</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.329659</v>
+        <v>0.884563</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.198387</v>
+        <v>0.803132</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.06811</v>
+        <v>0.792336</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.036367</v>
+        <v>0.112117</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.021122</v>
+        <v>0.096872</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.020067</v>
+        <v>0.095817</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.021494</v>
+        <v>0.09199400000000001</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.01768</v>
+        <v>0.12543</v>
       </c>
     </row>
     <row r="8">
@@ -1370,10 +1370,10 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.354735</v>
+        <v>-0.354735</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.184516</v>
+        <v>-0.305432</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -2343,7 +2343,7 @@
         <v>-7.709731494394967</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-4.132113140659938</v>
+        <v>-6.839946567116383</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -3930,19 +3930,19 @@
         <v>0</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>0.884719</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>1.121431</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>1.117928</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>1.205679</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>1.387337</v>
       </c>
       <c r="J56" s="3" t="n">
         <v>0</v>
@@ -3957,22 +3957,22 @@
         <v>0</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>1.584514</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0</v>
+        <v>1.971937</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0</v>
+        <v>1.960284</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0</v>
+        <v>1.953283</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>0</v>
+        <v>2.02456</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>0</v>
+        <v>2.03976</v>
       </c>
     </row>
     <row r="57">
@@ -3993,19 +3993,19 @@
         <v>0</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>0.202794</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>0.369968</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>0.545345</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>0.722398</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>0.845664</v>
       </c>
       <c r="J57" s="3" t="n">
         <v>0</v>
@@ -4020,22 +4020,22 @@
         <v>0</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>0</v>
+        <v>1.457691</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>0</v>
+        <v>1.506384</v>
       </c>
       <c r="P57" s="3" t="n">
-        <v>0</v>
+        <v>1.593255</v>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>0</v>
+        <v>1.694848</v>
       </c>
       <c r="R57" s="3" t="n">
-        <v>0</v>
+        <v>1.774445</v>
       </c>
       <c r="S57" s="3" t="n">
-        <v>0</v>
+        <v>1.886074</v>
       </c>
     </row>
     <row r="58">
@@ -7543,7 +7543,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.007164</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -7671,7 +7671,7 @@
         <v>0</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>0</v>
+        <v>-0.484947</v>
       </c>
       <c r="M114" s="3" t="n">
         <v>0</v>
@@ -8618,10 +8618,10 @@
         <v>16.57436</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>45.408108</v>
+        <v>44.708108</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>0.405601</v>
+        <v>-1.256231</v>
       </c>
       <c r="H129" s="1" t="inlineStr">
         <is>
@@ -8998,10 +8998,10 @@
         <v>-4.719869</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-4.777974</v>
+        <v>-4.077974</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-1.085261</v>
+        <v>0.5765709999999999</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-3.227358</v>
@@ -23764,7 +23764,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -27404,7 +27408,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -28032,7 +28040,11 @@
           <t>Deferred income tax expenses (recovery)</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -29140,7 +29152,11 @@
           <t>Net cash generated from investing activities</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -29454,7 +29470,11 @@
           <t>Deferred income tax expenses</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -30186,7 +30206,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -34146,7 +34170,11 @@
           <t>Acquisition of investments</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -35706,7 +35734,11 @@
           <t>Acquisition of investments (note 9)</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -35812,7 +35844,11 @@
           <t>Proceeds from disposition of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -37154,7 +37190,11 @@
           <t>Net cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -41970,7 +42010,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -44794,7 +44838,11 @@
           <t>- future income tax recovery</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -46848,7 +46896,11 @@
           <t>Directors' fees (note 15)</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -52800,7 +52852,11 @@
           <t>Directors' fees</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
           <t>-</t>
@@ -54120,7 +54176,11 @@
           <t>Field office expenses</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
@@ -57238,7 +57298,11 @@
           <t>Directors' fees</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E470" t="inlineStr">
         <is>
           <t>-</t>
@@ -57340,7 +57404,11 @@
           <t>Field office expenses</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E471" t="inlineStr">
         <is>
           <t>-</t>
@@ -60452,7 +60520,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
           <t>-</t>
@@ -62224,7 +62296,11 @@
           <t>Future income tax recovery (note 8)</t>
         </is>
       </c>
-      <c r="D518" t="inlineStr"/>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E518" t="inlineStr">
         <is>
           <t>-</t>
@@ -63046,7 +63122,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D526" t="inlineStr"/>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E526" s="5" t="n">
         <v>0.056833</v>
       </c>
@@ -63768,7 +63848,11 @@
           <t>Future income tax recovery (Note 8)</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E533" t="inlineStr">
         <is>
           <t>-</t>
